--- a/outputs/billing_Youstina_Ayman.xlsx
+++ b/outputs/billing_Youstina_Ayman.xlsx
@@ -426,7 +426,7 @@
     </row>
     <row r="7">
       <c r="H7" s="1">
-        <v>NaN</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10">
